--- a/output/var-dict/var-dict.xlsx
+++ b/output/var-dict/var-dict.xlsx
@@ -110,8 +110,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" id="1" name="Table1" displayName="Table1" ref="A1:I91" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" id="1" name="Table1" displayName="Table1" ref="A1:I107" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I107"/>
   <tableColumns count="9">
     <tableColumn id="1" name="pos"/>
     <tableColumn id="2" name="variable"/>
@@ -444,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="6.621"/>
@@ -872,7 +872,7 @@
       <c r="H13" s="10"/>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>M0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3294,24 +3294,24 @@
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>fct</t>
         </is>
       </c>
       <c r="E84" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>0 ; 1</t>
-        </is>
-      </c>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G84" s="10"/>
       <c r="H84" s="10"/>
-      <c r="I84" s="11"/>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="10">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>n_recidive_site_meta</t>
+          <t>total_ei_asthenie</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Nombre de sites métastatiques</t>
+          <t>Asthénie grade 3-4</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -3333,18 +3333,18 @@
         </is>
       </c>
       <c r="E85" s="10">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="G85" s="10"/>
       <c r="H85" s="10"/>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>1 ; &gt;=2</t>
+          <t>Non ; Oui</t>
         </is>
       </c>
     </row>
@@ -3354,28 +3354,34 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>os_event</t>
+          <t>total_ei_dig</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Décès toutes causes</t>
+          <t>Diarrhée grade 3-4</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>bin</t>
-        </is>
-      </c>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10" t="inlineStr">
-        <is>
-          <t>0 ; 1</t>
-        </is>
-      </c>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E86" s="10">
+        <v>5</v>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G86" s="10"/>
       <c r="H86" s="10"/>
-      <c r="I86" s="11"/>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="10">
@@ -3383,32 +3389,34 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>os_tte</t>
+          <t>total_ei_vom</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Délai entre la chirurgie et le décès toutes causes, mois</t>
+          <t>Nausées/vomissement grade 3-4</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10" t="inlineStr">
-        <is>
-          <t>0,4 ; 53,1</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>12,9 ; 19,2 ; 29,6</t>
-        </is>
-      </c>
-      <c r="I87" s="11"/>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E87" s="10">
+        <v>5</v>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G87" s="10"/>
+      <c r="H87" s="10"/>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10">
@@ -3416,32 +3424,34 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>os_tte_diag</t>
+          <t>total_ei_neutrop</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Délai entre le diagnostic et le décès toutes causes, mois</t>
+          <t>Neutropénie grade 3-4</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10" t="inlineStr">
-        <is>
-          <t>3,9 ; 58,9</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>16,1 ; 23,8 ; 34,5</t>
-        </is>
-      </c>
-      <c r="I88" s="11"/>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E88" s="10">
+        <v>5</v>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G88" s="10"/>
+      <c r="H88" s="10"/>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="10">
@@ -3449,28 +3459,34 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>pfs_event</t>
+          <t>total_ei_neuro</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Récidive ou décès toutes causes</t>
+          <t>Neurotoxicité grade 3-4</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>bin</t>
-        </is>
-      </c>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10" t="inlineStr">
-        <is>
-          <t>0 ; 1</t>
-        </is>
-      </c>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E89" s="10">
+        <v>5</v>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G89" s="10"/>
       <c r="H89" s="10"/>
-      <c r="I89" s="11"/>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="10">
@@ -3478,32 +3494,34 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>pfs_tte</t>
+          <t>total_ei_cytolyse</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Délai entre la chirurgie et la récidive ou le décès toutes causes, mois</t>
+          <t>Cytolyse/cholestase grade 3-4</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10" t="inlineStr">
-        <is>
-          <t>0,4 ; 50,1</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>8,5 ; 13,7 ; 22,4</t>
-        </is>
-      </c>
-      <c r="I90" s="11"/>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E90" s="10">
+        <v>6</v>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="G90" s="10"/>
+      <c r="H90" s="10"/>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="10">
@@ -3511,12 +3529,12 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>pfs_cause</t>
+          <t>total_adapt</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Premier évènement</t>
+          <t>Adaptation de doses</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -3524,11 +3542,547 @@
           <t>fct</t>
         </is>
       </c>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
+      <c r="E91" s="10">
+        <v>3</v>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
       <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10">
+        <v>91</v>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>total_adapt_pct</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>Pourcentage d'adaptation</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E92" s="10">
+        <v>5</v>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G92" s="10"/>
+      <c r="H92" s="10"/>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Pas d'adaptation ; &lt;=20% ; &gt;20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10">
+        <v>92</v>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>total_dose_5fu</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Dernière dose reçue : 5-FU, %</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="E93" s="10">
+        <v>5</v>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>0 ; 100</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>75 ; 80 ; 100</t>
+        </is>
+      </c>
+      <c r="I93" s="11"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10">
+        <v>93</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>total_dose_irino</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>Dernière dose reçue : Irinotécan, %</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="E94" s="10">
+        <v>5</v>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>0 ; 100</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>50 ; 70 ; 80</t>
+        </is>
+      </c>
+      <c r="I94" s="11"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="10">
+        <v>94</v>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>total_dose_oxali</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Dernière dose reçue : Oxaliplatine, %</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="E95" s="10">
+        <v>5</v>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>0 ; 100</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>0 ; 25 ; 70</t>
+        </is>
+      </c>
+      <c r="I95" s="11"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="10">
+        <v>95</v>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>total_adapt_c4</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>Adaptation de dose à C4</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E96" s="10">
+        <v>9</v>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="G96" s="10"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Non ; &lt;=20% ; &gt;20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10">
+        <v>96</v>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>total_adapt_c8</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>Adaptation de dose à C8</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E97" s="10">
+        <v>40</v>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>38,8%</t>
+        </is>
+      </c>
+      <c r="G97" s="10"/>
+      <c r="H97" s="10"/>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Non ; &lt;=20% ; &gt;20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10">
+        <v>97</v>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>total_adapt_c12</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>Adaptation de dose à C12</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E98" s="10">
+        <v>68</v>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>66,0%</t>
+        </is>
+      </c>
+      <c r="G98" s="10"/>
+      <c r="H98" s="10"/>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Non ; &lt;=20% ; &gt;20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10">
+        <v>98</v>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>recidive_none</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>Type de récidive : Aucune</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E99" s="10"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10">
+        <v>99</v>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>recidive_loc</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>Type de récidive : Locale</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E100" s="10"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="10"/>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10">
+        <v>100</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>recidive_meta</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Type de récidive : Métastatique</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E101" s="10"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="10"/>
+      <c r="H101" s="10"/>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>Non ; Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10">
+        <v>101</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>os_event</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>Décès toutes causes</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>bin</t>
+        </is>
+      </c>
+      <c r="E102" s="10"/>
+      <c r="F102" s="10"/>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>0 ; 1</t>
+        </is>
+      </c>
+      <c r="H102" s="10"/>
+      <c r="I102" s="11"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10">
+        <v>102</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>os_tte</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Délai entre la chirurgie et le décès toutes causes, mois</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="E103" s="10"/>
+      <c r="F103" s="10"/>
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t>0,4 ; 53,1</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>12,9 ; 19,2 ; 29,6</t>
+        </is>
+      </c>
+      <c r="I103" s="11"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="10">
+        <v>103</v>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>os_tte_diag</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>Délai entre le diagnostic et le décès toutes causes, mois</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="E104" s="10"/>
+      <c r="F104" s="10"/>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>3,9 ; 58,9</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>16,1 ; 23,8 ; 34,5</t>
+        </is>
+      </c>
+      <c r="I104" s="11"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10">
+        <v>104</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>pfs_event</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>Récidive ou décès toutes causes</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>bin</t>
+        </is>
+      </c>
+      <c r="E105" s="10"/>
+      <c r="F105" s="10"/>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>0 ; 1</t>
+        </is>
+      </c>
+      <c r="H105" s="10"/>
+      <c r="I105" s="11"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="10">
+        <v>105</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>pfs_tte</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>Délai entre la chirurgie et la récidive ou le décès toutes causes, mois</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="E106" s="10"/>
+      <c r="F106" s="10"/>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>0,4 ; 50,1</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>8,5 ; 13,7 ; 22,4</t>
+        </is>
+      </c>
+      <c r="I106" s="11"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="10">
+        <v>106</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>pfs_cause</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>Premier évènement</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>fct</t>
+        </is>
+      </c>
+      <c r="E107" s="10"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="10"/>
+      <c r="H107" s="10"/>
+      <c r="I107" s="11" t="inlineStr">
         <is>
           <t>Censure ; Récidive ; Décès sans récidive</t>
         </is>
